--- a/доки/ЛР1_паспорт.xlsx
+++ b/доки/ЛР1_паспорт.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Паспорт проекта" sheetId="1" state="visible" r:id="rId3"/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t xml:space="preserve">Рабочее название проекта</t>
   </si>
@@ -165,13 +165,10 @@
     <t xml:space="preserve">Ссылка на репозиторий</t>
   </si>
   <si>
-    <t>https://github.com/[добавить_при_наличии]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Проблема, которую решает проект</t>
   </si>
   <si>
-    <t xml:space="preserve">Моя целевая аудитория — дизайнеры, контент-мейкеры, SMM-специалисты, небольшие интернет-магазины и продавцы на маркетплейсах. В данный момент они сталкиваются с тем, что быстро выполнить качественную стилизацию и базовое редактирование изображений в едином визуальном стиле с использованием собственных референсов затруднительно: существующие сервисы либо перегружены лишними функциями, либо ограничивают работу с пользовательским стилем, либо требуют длительной ручной обработки. Из-за этого пользователи теряют время на подготовку визуального контента, несут дополнительные затраты на ручной дизайн и не могут быстро получать готовые изображения в едином фирменном стиле.</t>
+    <t xml:space="preserve">Дизайнеры, контент-мейкеры, SMM-специалисты, небольшие интернет-магазины и продавцы на маркетплейсах. В данный момент они сталкиваются с тем, что быстро выполнить качественную стилизацию и базовое редактирование изображений в едином визуальном стиле с использованием собственных референсов затруднительно: существующие сервисы либо перегружены лишними функциями, либо ограничивают работу с пользовательским стилем, либо требуют длительной ручной обработки. Из-за этого пользователи теряют время на подготовку визуального контента, несут дополнительные затраты на ручной дизайн и не могут быстро получать готовые изображения в едином фирменном стиле.</t>
   </si>
   <si>
     <t xml:space="preserve">Цель проекта</t>
@@ -422,41 +419,7 @@
     <t>8=7*6</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Разработка программного обеспечения _______________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Руководитель разработки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Технический лидер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инженер-разработчик (GUI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инженер-разработчик (back-end)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Системный аналитик</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Технический писатель</t>
-  </si>
-  <si>
-    <t>DevOps-инженер</t>
-  </si>
-  <si>
-    <t>QA-инженер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI/UX дизайнер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Администратор проекта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Специалист по ИБ</t>
+    <t xml:space="preserve">Разработка программного обеспечения</t>
   </si>
   <si>
     <t>ИТОГО:</t>
@@ -511,7 +474,6 @@
   <fonts count="9">
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -521,18 +483,24 @@
     <font>
       <b/>
       <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="12.000000"/>
-      <color indexed="64"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12.000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -541,18 +509,7 @@
       <name val="Times New Roman"/>
     </font>
     <font>
-      <i/>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
       <sz val="11.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -569,7 +526,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="21">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -593,6 +550,43 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="none"/>
       <right style="none"/>
       <top style="none"/>
@@ -703,10 +697,10 @@
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color theme="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color theme="1"/>
       </top>
       <bottom style="thin">
@@ -718,10 +712,10 @@
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="thin">
@@ -802,7 +796,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="74">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -813,8 +807,14 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf fontId="3" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -844,10 +844,10 @@
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -858,30 +858,52 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="4" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="5" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="2" borderId="1" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -889,20 +911,19 @@
     <xf fontId="5" fillId="0" borderId="11" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="2" borderId="1" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="2" borderId="1" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="12" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="5" fillId="0" borderId="1" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="14" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="15" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -917,69 +938,69 @@
     <xf fontId="5" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="2" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="8" fillId="2" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="13" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="16" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="5" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="8" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="2" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="2" borderId="9" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="2" borderId="12" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="2" borderId="12" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="14" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="2" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="8" fillId="2" borderId="12" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="2" borderId="14" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="5" fillId="2" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="2" borderId="12" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="2" borderId="14" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="4" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="15" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="2" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf fontId="4" fillId="2" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="15" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="2" borderId="18" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="18" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1004,7 +1025,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Unknown Author" id="{33F0173F-CD40-2061-EAEA-F398077D71DF}"/>
+  <person displayName="Unknown Author" id="{C5E2AD0C-2814-4475-B543-4AD88AAFF4E8}"/>
 </personList>
 </file>
 
@@ -1397,7 +1418,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A18" personId="{33F0173F-CD40-2061-EAEA-F398077D71DF}" id="{0092005F-0094-4EF0-B834-007800D600EF}" done="0">
+  <threadedComment ref="A18" personId="{C5E2AD0C-2814-4475-B543-4AD88AAFF4E8}" id="{0092005F-0094-4EF0-B834-007800D600EF}" done="0">
     <text xml:space="preserve">Наталья Заборовская:
 пречислить верхнеуровневые риски - 3-5
 </text>
@@ -1407,7 +1428,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A1" personId="{33F0173F-CD40-2061-EAEA-F398077D71DF}" id="{006900B0-009C-4977-B237-00B400100078}" done="0">
+  <threadedComment ref="A1" personId="{C5E2AD0C-2814-4475-B543-4AD88AAFF4E8}" id="{006900B0-009C-4977-B237-00B400100078}" done="0">
     <text xml:space="preserve">Наталья Заборовская:
 Перечислить состав команды, з/п в месяц и продолжительность задействования в проекте по каждому сотруднику
 </text>
@@ -1417,7 +1438,7 @@
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E3" personId="{33F0173F-CD40-2061-EAEA-F398077D71DF}" id="{00AD0062-0064-4CB8-9ABA-000200C6002B}" done="0">
+  <threadedComment ref="E3" personId="{C5E2AD0C-2814-4475-B543-4AD88AAFF4E8}" id="{00AD0062-0064-4CB8-9ABA-000200C6002B}" done="0">
     <text xml:space="preserve">Наталья Заборовская:
 (Количество × Стоимость) × коэффициент удорожания
 </text>
@@ -1427,7 +1448,7 @@
 
 <file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A27" personId="{33F0173F-CD40-2061-EAEA-F398077D71DF}" id="{005E0054-00E7-4D6F-AD37-0077001A00E3}" done="0">
+  <threadedComment ref="A27" personId="{C5E2AD0C-2814-4475-B543-4AD88AAFF4E8}" id="{005E0054-00E7-4D6F-AD37-0077001A00E3}" done="0">
     <text xml:space="preserve">Наталья Заборовская:
 Итоговая стоимость по техническим ограничениям
 </text>
@@ -1445,7 +1466,7 @@
     <col customWidth="1" min="4" max="4" width="31.77734375"/>
   </cols>
   <sheetData>
-    <row r="1" ht="180">
+    <row r="1" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1460,7 +1481,7 @@
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" ht="45">
+    <row r="2" ht="16.5">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1475,13 +1496,11 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" ht="75">
+    <row r="3" ht="16.5">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -1490,12 +1509,12 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" ht="409.5">
+    <row r="4" ht="115.5">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -1507,10 +1526,10 @@
     </row>
     <row r="5" ht="49.5" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -1520,14 +1539,14 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" ht="41.950000000000003" customHeight="1">
+    <row r="6" ht="15">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1535,13 +1554,11 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" ht="50.75" customHeight="1">
+    <row r="7" ht="15">
       <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -1550,9 +1567,7 @@
     </row>
     <row r="8" ht="26.949999999999999" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -1561,24 +1576,20 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" ht="45.700000000000003" customHeight="1">
+    <row r="9" ht="15">
       <c r="A9" s="1"/>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B9" s="5"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
+      <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" ht="34.450000000000003" customHeight="1">
+    <row r="10" ht="15">
       <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B10" s="5"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1589,9 +1600,7 @@
     </row>
     <row r="11" ht="31.25" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B11" s="5"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -1600,11 +1609,9 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" ht="109.5" customHeight="1">
+    <row r="12" ht="15">
       <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B12" s="6"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1613,12 +1620,12 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" ht="409.5">
+    <row r="13" ht="99">
       <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1628,12 +1635,12 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" ht="30">
+    <row r="14" ht="16.5">
       <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1643,12 +1650,12 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" ht="30">
+    <row r="15" ht="16.5">
       <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1658,12 +1665,12 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" ht="409.5">
+    <row r="16" ht="99">
       <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1675,9 +1682,11 @@
     </row>
     <row r="17" ht="16.5">
       <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="7"/>
+        <v>19</v>
+      </c>
+      <c r="B17" s="9">
+        <v>2451262.8399999999</v>
+      </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1686,12 +1695,12 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" ht="409.5">
+    <row r="18" ht="115.5">
       <c r="A18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1701,12 +1710,12 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" ht="345">
+    <row r="19" ht="49.5">
       <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1716,12 +1725,12 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" ht="120">
+    <row r="20" ht="16.5">
       <c r="A20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1732,8 +1741,9 @@
       <c r="I20" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:A12"/>
+    <mergeCell ref="B6:B12"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1753,140 +1763,140 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="8" t="s">
+    </row>
+    <row r="2" ht="47">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" ht="47">
-      <c r="A2" s="9">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="9" t="s">
+    </row>
+    <row r="3" ht="15.6">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" ht="15.6">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="9" t="s">
+    </row>
+    <row r="4" ht="15.6">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" ht="15.6">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="9" t="s">
+    </row>
+    <row r="5" ht="15.6">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" ht="15.6">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="9" t="s">
+    </row>
+    <row r="6" ht="15.6">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" ht="15.6">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="7" ht="15.6">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
     </row>
     <row r="8" ht="15.6">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
     </row>
     <row r="9" ht="15.6">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
     </row>
     <row r="10" ht="15.6">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
     </row>
     <row r="11" ht="15.050000000000001">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
     </row>
     <row r="12" ht="15.050000000000001">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
     </row>
     <row r="13" ht="15.050000000000001">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
     </row>
     <row r="14" ht="15.050000000000001">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
     </row>
     <row r="15" ht="15.050000000000001">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
     </row>
     <row r="16" ht="15.050000000000001">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
     </row>
     <row r="17" ht="15.050000000000001">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
     </row>
     <row r="18" ht="15.050000000000001">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
     </row>
     <row r="19" ht="15.050000000000001">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
     </row>
     <row r="20" ht="15.050000000000001">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1909,245 +1919,245 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="12" t="s">
+    </row>
+    <row r="2" ht="47">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" ht="47">
-      <c r="A2" s="9">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D2" s="11">
+        <v>100</v>
+      </c>
+      <c r="E2" s="15">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="3" ht="15.6">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C3" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D3" s="11">
+        <v>90</v>
+      </c>
+      <c r="E3" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="11">
+        <v>1</v>
+      </c>
+      <c r="D4" s="11">
+        <v>140</v>
+      </c>
+      <c r="E4" s="15">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" ht="15.6">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11">
+        <v>130</v>
+      </c>
+      <c r="E5" s="15">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" ht="15.6">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11">
+        <v>160</v>
+      </c>
+      <c r="E6" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="15.6">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11">
         <v>100</v>
       </c>
-      <c r="E2" s="13">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="3" ht="15.6">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="9">
+      <c r="E7" s="15">
         <v>1</v>
       </c>
-      <c r="D3" s="9">
+    </row>
+    <row r="8" ht="15.6">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11">
         <v>90</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E8" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15.6">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="9">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9">
-        <v>140</v>
-      </c>
-      <c r="E4" s="13">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5" ht="15.6">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="9">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9">
-        <v>130</v>
-      </c>
-      <c r="E5" s="13">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6" ht="15.6">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="9">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9">
-        <v>160</v>
-      </c>
-      <c r="E6" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" ht="15.6">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="9">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9">
-        <v>100</v>
-      </c>
-      <c r="E7" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="15.6">
-      <c r="A8" s="9">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9">
-        <v>90</v>
-      </c>
-      <c r="E8" s="13">
-        <v>1</v>
-      </c>
-    </row>
     <row r="9" ht="15.6">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
     </row>
     <row r="10" ht="15.6">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
     </row>
     <row r="11" ht="15.6">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
     </row>
     <row r="12" ht="15.6">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
     </row>
     <row r="13" ht="15.6">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
     </row>
     <row r="14" ht="15.6">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" ht="15.6">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" ht="15.6">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" ht="15.6">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18" ht="15.6">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19" ht="15.6">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20" ht="15.6">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="21" ht="15.6">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
     </row>
     <row r="22" ht="15.6">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
     </row>
     <row r="23" ht="15.6">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -2169,184 +2179,184 @@
   </cols>
   <sheetData>
     <row r="1" ht="52" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" ht="52.549999999999997" customHeight="1">
+      <c r="A2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" ht="52.549999999999997" customHeight="1">
-      <c r="A2" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" ht="30">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" ht="30">
-      <c r="A3" s="9">
+      <c r="C3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="D3" s="11">
+        <v>120000</v>
+      </c>
+      <c r="E3" s="11">
+        <v>144000</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" ht="30">
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C4" s="11">
+        <v>2</v>
+      </c>
+      <c r="D4" s="11">
+        <v>80000</v>
+      </c>
+      <c r="E4" s="11">
+        <v>192000</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" ht="45">
+      <c r="A5" s="11">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="11">
+        <v>25000</v>
+      </c>
+      <c r="E5" s="11">
+        <v>60000</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" ht="30">
+      <c r="A6" s="11">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="11">
+        <v>5000</v>
+      </c>
+      <c r="E6" s="11">
+        <v>18000</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" ht="45">
+      <c r="A7" s="11">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="11">
+        <v>10800</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" ht="15.6">
+      <c r="A8" s="11">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="11">
         <v>1</v>
       </c>
-      <c r="D3" s="9">
-        <v>120000</v>
-      </c>
-      <c r="E3" s="9">
-        <v>144000</v>
-      </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" ht="30">
-      <c r="A4" s="9">
-        <v>2</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="9">
-        <v>2</v>
-      </c>
-      <c r="D4" s="9">
-        <v>80000</v>
-      </c>
-      <c r="E4" s="9">
-        <v>192000</v>
-      </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="45">
-      <c r="A5" s="9">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="9">
-        <v>25000</v>
-      </c>
-      <c r="E5" s="9">
-        <v>60000</v>
-      </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" ht="30">
-      <c r="A6" s="9">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="D8" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E8" s="11">
+        <v>3600</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" ht="30">
+      <c r="A9" s="11">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11">
         <v>5000</v>
       </c>
-      <c r="E6" s="9">
-        <v>18000</v>
-      </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" ht="45">
-      <c r="A7" s="9">
-        <v>5</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="9">
-        <v>3000</v>
-      </c>
-      <c r="E7" s="9">
-        <v>10800</v>
-      </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" ht="15.6">
-      <c r="A8" s="9">
-        <v>6</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="9">
+      <c r="E9" s="11">
+        <v>6000</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" ht="30">
+      <c r="A10" s="11">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="11">
         <v>1</v>
       </c>
-      <c r="D8" s="9">
-        <v>3000</v>
-      </c>
-      <c r="E8" s="9">
-        <v>3600</v>
-      </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="30">
-      <c r="A9" s="9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="9">
-        <v>5000</v>
-      </c>
-      <c r="E9" s="9">
-        <v>6000</v>
-      </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" ht="30">
-      <c r="A10" s="9">
-        <v>8</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="11">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="11">
+        <v>12000</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" ht="15.6">
+      <c r="A11" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="9">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9">
-        <v>10000</v>
-      </c>
-      <c r="E10" s="9">
-        <v>12000</v>
-      </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" ht="15.6">
-      <c r="A11" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="10">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="12">
         <f>SUM(E3:E10)</f>
         <v>446400</v>
       </c>
@@ -2394,683 +2404,677 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="8.90234375" defaultRowHeight="15.649999618530273"/>
+  <sheetFormatPr defaultColWidth="8.90234375" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="0" min="1" max="1" style="17" width="8.8999996185302734"/>
-    <col customWidth="1" min="2" max="2" style="17" width="26.899999618530273"/>
-    <col customWidth="1" min="3" max="3" style="17" width="27.440000534057617"/>
-    <col customWidth="1" min="4" max="4" style="17" width="16.450000762939453"/>
-    <col customWidth="1" min="5" max="5" style="17" width="19.540000915527344"/>
-    <col customWidth="1" min="6" max="6" style="17" width="16.450000762939453"/>
-    <col customWidth="1" min="7" max="7" style="17" width="27.629999160766602"/>
-    <col customWidth="1" min="8" max="8" style="17" width="23.620000839233398"/>
-    <col customWidth="1" min="9" max="9" style="17" width="19.440000534057617"/>
-    <col customWidth="1" min="10" max="10" style="17" width="13.350000381469727"/>
-    <col customWidth="1" min="11" max="11" style="17" width="2.809999942779541"/>
-    <col customWidth="0" min="12" max="257" style="17" width="8.8999996185302734"/>
+    <col customWidth="0" min="1" max="1" style="19" width="8.8999996185302734"/>
+    <col customWidth="1" min="2" max="2" style="19" width="26.899999618530273"/>
+    <col customWidth="1" min="3" max="3" style="19" width="27.440000534057617"/>
+    <col customWidth="1" min="4" max="4" style="19" width="16.450000762939453"/>
+    <col customWidth="1" min="5" max="5" style="19" width="19.540000915527344"/>
+    <col customWidth="1" min="6" max="6" style="19" width="16.450000762939453"/>
+    <col customWidth="1" min="7" max="7" style="19" width="27.629999160766602"/>
+    <col customWidth="1" min="8" max="8" style="19" width="23.620000839233398"/>
+    <col customWidth="1" min="9" max="9" style="19" width="19.440000534057617"/>
+    <col customWidth="1" min="10" max="10" style="19" width="13.350000381469727"/>
+    <col customWidth="1" min="11" max="11" style="19" width="2.809999942779541"/>
+    <col customWidth="0" min="12" max="257" style="19" width="8.8999996185302734"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6">
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" ht="15.6">
+      <c r="A3" s="21" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" ht="15.6">
-      <c r="A3" s="19" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="22"/>
+    </row>
+    <row r="4" ht="31.5" customHeight="1">
+      <c r="A4" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="20"/>
-    </row>
-    <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" s="21" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="22"/>
+    </row>
+    <row r="5" ht="15.6">
+      <c r="A5" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="20"/>
-    </row>
-    <row r="5" ht="15.6">
-      <c r="A5" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="20"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" ht="16.25"/>
     <row r="7" ht="43.5" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23" t="s">
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23" t="s">
+      <c r="H7" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="I7" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="J7" s="26"/>
+    </row>
+    <row r="8" ht="43.5" customHeight="1">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="24"/>
-    </row>
-    <row r="8" ht="43.5" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="23" t="s">
+      <c r="E8" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="F8" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26"/>
+    </row>
+    <row r="9" ht="16.25">
+      <c r="A9" s="27">
+        <v>1</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28">
+        <v>2</v>
+      </c>
+      <c r="D9" s="28">
+        <v>3</v>
+      </c>
+      <c r="E9" s="28">
+        <v>4</v>
+      </c>
+      <c r="F9" s="28">
+        <v>5</v>
+      </c>
+      <c r="G9" s="28">
+        <v>6</v>
+      </c>
+      <c r="H9" s="28">
+        <v>7</v>
+      </c>
+      <c r="I9" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="24"/>
-    </row>
-    <row r="9" ht="16.25">
-      <c r="A9" s="25">
+      <c r="J9" s="30"/>
+    </row>
+    <row r="10" ht="15">
+      <c r="A10" s="31">
         <v>1</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26">
+      <c r="B10" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="31">
+        <v>1</v>
+      </c>
+      <c r="E10" s="33">
+        <v>46063</v>
+      </c>
+      <c r="F10" s="34">
+        <v>46139</v>
+      </c>
+      <c r="G10" s="31">
+        <v>440</v>
+      </c>
+      <c r="H10" s="31">
+        <v>568</v>
+      </c>
+      <c r="I10" s="35">
+        <f>G10*H10</f>
+        <v>249920</v>
+      </c>
+      <c r="J10" s="30"/>
+    </row>
+    <row r="11" ht="30">
+      <c r="A11" s="31">
         <v>2</v>
       </c>
-      <c r="D9" s="26">
+      <c r="B11" s="32"/>
+      <c r="C11" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="31">
+        <v>1</v>
+      </c>
+      <c r="E11" s="33">
+        <v>46063</v>
+      </c>
+      <c r="F11" s="34">
+        <v>46090</v>
+      </c>
+      <c r="G11" s="31">
+        <v>176</v>
+      </c>
+      <c r="H11" s="31">
+        <v>511</v>
+      </c>
+      <c r="I11" s="35">
+        <f>G11*H11</f>
+        <v>89936</v>
+      </c>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" ht="16.25">
+      <c r="A12" s="31">
         <v>3</v>
       </c>
-      <c r="E9" s="26">
+      <c r="B12" s="32"/>
+      <c r="C12" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="31">
+        <v>1</v>
+      </c>
+      <c r="E12" s="33">
+        <v>46091</v>
+      </c>
+      <c r="F12" s="34">
+        <v>46135</v>
+      </c>
+      <c r="G12" s="31">
+        <v>264</v>
+      </c>
+      <c r="H12" s="31">
+        <v>795</v>
+      </c>
+      <c r="I12" s="35">
+        <f>G12*H12</f>
+        <v>209880</v>
+      </c>
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" ht="16.25">
+      <c r="A13" s="31">
         <v>4</v>
       </c>
-      <c r="F9" s="26">
+      <c r="B13" s="32"/>
+      <c r="C13" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="31">
+        <v>1</v>
+      </c>
+      <c r="E13" s="33">
+        <v>46091</v>
+      </c>
+      <c r="F13" s="34">
+        <v>46135</v>
+      </c>
+      <c r="G13" s="37">
+        <v>264</v>
+      </c>
+      <c r="H13" s="31">
+        <v>739</v>
+      </c>
+      <c r="I13" s="35">
+        <f>G13*H13</f>
+        <v>195096</v>
+      </c>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" ht="16.25">
+      <c r="A14" s="31">
         <v>5</v>
       </c>
-      <c r="G9" s="26">
+      <c r="B14" s="32"/>
+      <c r="C14" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="31">
+        <v>1</v>
+      </c>
+      <c r="E14" s="33">
+        <v>46077</v>
+      </c>
+      <c r="F14" s="34">
+        <v>46139</v>
+      </c>
+      <c r="G14" s="37">
+        <v>352</v>
+      </c>
+      <c r="H14" s="31">
+        <v>909</v>
+      </c>
+      <c r="I14" s="35">
+        <f>G14*H14</f>
+        <v>319968</v>
+      </c>
+      <c r="J14" s="36"/>
+      <c r="K14" s="19"/>
+    </row>
+    <row r="15" ht="16.25">
+      <c r="A15" s="31">
         <v>6</v>
       </c>
-      <c r="H9" s="26">
+      <c r="B15" s="32"/>
+      <c r="C15" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="31">
+        <v>1</v>
+      </c>
+      <c r="E15" s="33">
+        <v>46077</v>
+      </c>
+      <c r="F15" s="34">
+        <v>46104</v>
+      </c>
+      <c r="G15" s="37">
+        <v>176</v>
+      </c>
+      <c r="H15" s="31">
+        <v>568</v>
+      </c>
+      <c r="I15" s="35">
+        <f>G15*H15</f>
+        <v>99968</v>
+      </c>
+      <c r="J15" s="36"/>
+      <c r="K15" s="19"/>
+    </row>
+    <row r="16" ht="16.25">
+      <c r="A16" s="31">
         <v>7</v>
       </c>
-      <c r="I9" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="28"/>
-    </row>
-    <row r="10" ht="47.450000000000003" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="30">
+      <c r="B16" s="32"/>
+      <c r="C16" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F10" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G10" s="30">
-        <v>100</v>
-      </c>
-      <c r="H10" s="30">
-        <v>900</v>
-      </c>
-      <c r="I10" s="33">
-        <f t="shared" ref="I10:I21" si="0">D10*G10*H10</f>
-        <v>90000</v>
-      </c>
-      <c r="J10" s="28"/>
-    </row>
-    <row r="11" ht="16.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="30">
-        <v>1</v>
-      </c>
-      <c r="E11" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F11" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G11" s="30">
-        <v>500</v>
-      </c>
-      <c r="H11" s="30">
-        <v>500</v>
-      </c>
-      <c r="I11" s="33">
-        <f t="shared" si="0"/>
-        <v>250000</v>
-      </c>
-      <c r="J11" s="34"/>
-    </row>
-    <row r="12" ht="16.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="30">
-        <v>1</v>
-      </c>
-      <c r="E12" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F12" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="33">
+      <c r="E16" s="33">
+        <v>46112</v>
+      </c>
+      <c r="F16" s="34">
+        <v>46139</v>
+      </c>
+      <c r="G16" s="37">
+        <v>176</v>
+      </c>
+      <c r="H16" s="31">
+        <v>511</v>
+      </c>
+      <c r="I16" s="35">
+        <f>G16*H16</f>
+        <v>89936</v>
+      </c>
+      <c r="J16" s="36"/>
+      <c r="K16" s="38"/>
+    </row>
+    <row r="17" ht="16.25">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="44">
+        <f t="shared" ref="I17:I21" si="0">D17*G17*H17</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="36"/>
+      <c r="K17" s="38"/>
+    </row>
+    <row r="18" ht="16.25">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="34"/>
-    </row>
-    <row r="13" ht="16.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="30">
-        <v>4</v>
-      </c>
-      <c r="E13" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F13" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="33">
+      <c r="J18" s="36"/>
+      <c r="K18" s="38"/>
+    </row>
+    <row r="19" ht="16.25">
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="34"/>
-    </row>
-    <row r="14" ht="16.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="30">
-        <v>4</v>
-      </c>
-      <c r="E14" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F14" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="33">
+      <c r="J19" s="36"/>
+      <c r="K19" s="38"/>
+    </row>
+    <row r="20" ht="16.25">
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="34"/>
-      <c r="K14" s="17"/>
-    </row>
-    <row r="15" ht="16.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="30">
-        <v>2</v>
-      </c>
-      <c r="E15" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F15" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G15" s="35"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="33">
+      <c r="J20" s="36"/>
+      <c r="K20" s="38"/>
+    </row>
+    <row r="21" ht="15.6">
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="34"/>
-      <c r="K15" s="17"/>
-    </row>
-    <row r="16" ht="16.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="30">
-        <v>1</v>
-      </c>
-      <c r="E16" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F16" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G16" s="35"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="34"/>
-      <c r="K16" s="36"/>
-    </row>
-    <row r="17" ht="16.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="30">
-        <v>2</v>
-      </c>
-      <c r="E17" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F17" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G17" s="35"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="34"/>
-      <c r="K17" s="36"/>
-    </row>
-    <row r="18" ht="16.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="30">
-        <v>3</v>
-      </c>
-      <c r="E18" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F18" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G18" s="35"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="34"/>
-      <c r="K18" s="36"/>
-    </row>
-    <row r="19" ht="16.25">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="30">
-        <v>1</v>
-      </c>
-      <c r="E19" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F19" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G19" s="35"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="36"/>
-    </row>
-    <row r="20" ht="16.25">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="30">
-        <v>1</v>
-      </c>
-      <c r="E20" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F20" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="36"/>
-    </row>
-    <row r="21" ht="15.6">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="30">
-        <v>1</v>
-      </c>
-      <c r="E21" s="31">
-        <v>45901</v>
-      </c>
-      <c r="F21" s="32">
-        <v>46174</v>
-      </c>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="38"/>
     </row>
     <row r="22" ht="30.699999999999999" customHeight="1">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="17"/>
+      <c r="A22" s="46"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="19"/>
     </row>
     <row r="23" ht="19.850000000000001" customHeight="1">
-      <c r="A23" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="46">
+      <c r="A23" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="55">
         <f>SUM(I10:I22)</f>
-        <v>340000</v>
-      </c>
-      <c r="K23" s="17"/>
+        <v>1254704</v>
+      </c>
+      <c r="K23" s="19"/>
     </row>
     <row r="24" ht="19.850000000000001" customHeight="1">
-      <c r="A24" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="17"/>
+      <c r="A24" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="19"/>
     </row>
     <row r="25" ht="19.850000000000001" customHeight="1">
-      <c r="A25" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="50">
+      <c r="A25" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="59">
         <f>I23</f>
-        <v>340000</v>
-      </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="51"/>
+        <v>1254704</v>
+      </c>
+      <c r="J25" s="30"/>
+      <c r="K25" s="60"/>
     </row>
     <row r="26" ht="19.449999999999999" customHeight="1">
-      <c r="A26" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="52">
+      <c r="A26" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="61">
         <f>I25*0.1</f>
-        <v>34000</v>
-      </c>
-      <c r="J26" s="53"/>
-      <c r="K26" s="54"/>
+        <v>125470.40000000001</v>
+      </c>
+      <c r="J26" s="62"/>
+      <c r="K26" s="63"/>
     </row>
     <row r="27" ht="19.449999999999999" customHeight="1">
-      <c r="A27" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="56">
+      <c r="A27" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65">
         <f>'Технические ограничения'!E11</f>
         <v>446400</v>
       </c>
-      <c r="J27" s="28"/>
-      <c r="K27" s="54"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="63"/>
     </row>
     <row r="28" ht="19.850000000000001" customHeight="1">
-      <c r="A28" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="55"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="56">
+      <c r="A28" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="64"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65">
         <v>0</v>
       </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="54"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="63"/>
     </row>
     <row r="29" ht="19.850000000000001" customHeight="1">
-      <c r="A29" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="50">
+      <c r="A29" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="66"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="59">
         <f>I25+I26+I27+I28</f>
-        <v>820400</v>
-      </c>
-      <c r="J29" s="28"/>
-      <c r="K29" s="51"/>
+        <v>1826574.3999999999</v>
+      </c>
+      <c r="J29" s="30"/>
+      <c r="K29" s="60"/>
     </row>
     <row r="30" ht="19.850000000000001" customHeight="1">
-      <c r="A30" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="56">
+      <c r="A30" s="64" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="65">
         <v>0</v>
       </c>
-      <c r="J30" s="28"/>
-      <c r="K30" s="54"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="63"/>
     </row>
     <row r="31" ht="19.850000000000001" customHeight="1">
-      <c r="A31" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="58"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="56">
+      <c r="A31" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="65">
         <f>I29+I30</f>
-        <v>820400</v>
-      </c>
-      <c r="J31" s="28"/>
-      <c r="K31" s="54"/>
+        <v>1826574.3999999999</v>
+      </c>
+      <c r="J31" s="30"/>
+      <c r="K31" s="63"/>
     </row>
     <row r="32" ht="19.850000000000001" customHeight="1">
-      <c r="A32" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="56">
+      <c r="A32" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="58"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="65">
         <f>I31*0.1</f>
-        <v>82040</v>
-      </c>
-      <c r="J32" s="53"/>
-      <c r="K32" s="54"/>
-      <c r="Q32" s="59"/>
+        <v>182657.44</v>
+      </c>
+      <c r="J32" s="62"/>
+      <c r="K32" s="63"/>
+      <c r="Q32" s="68"/>
     </row>
     <row r="33" ht="19.850000000000001" customHeight="1">
-      <c r="A33" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="60"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="61">
+      <c r="A33" s="69" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="70">
         <f>I32+I31</f>
-        <v>902440</v>
-      </c>
-      <c r="J33" s="59"/>
-      <c r="K33" s="51"/>
+        <v>2009231.8399999999</v>
+      </c>
+      <c r="J33" s="68"/>
+      <c r="K33" s="60"/>
     </row>
     <row r="34" ht="19.449999999999999" customHeight="1">
-      <c r="A34" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="62"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="56">
+      <c r="A34" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="65">
         <f>I33*0.22</f>
-        <v>198536.79999999999</v>
-      </c>
-      <c r="J34" s="59"/>
-      <c r="K34" s="51"/>
+        <v>442031.0048</v>
+      </c>
+      <c r="J34" s="68"/>
+      <c r="K34" s="60"/>
     </row>
     <row r="35" ht="16.25" customHeight="1">
-      <c r="A35" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" s="63"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="64">
+      <c r="A35" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="73">
         <f>I33+0.22*I33</f>
-        <v>1100976.8</v>
+        <v>2451262.8448000001</v>
       </c>
     </row>
     <row r="36" ht="15.6">
-      <c r="K36" s="17"/>
+      <c r="K36" s="19"/>
     </row>
     <row r="37" ht="15.6">
-      <c r="K37" s="17"/>
+      <c r="K37" s="19"/>
     </row>
     <row r="40" ht="34.450000000000003" customHeight="1"/>
   </sheetData>
@@ -3086,7 +3090,7 @@
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
-    <mergeCell ref="A10:B21"/>
+    <mergeCell ref="B10:B16"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A25:H25"/>
